--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9751801</v>
+        <v>4787845</v>
       </c>
       <c r="L2" t="n">
-        <v>6114889</v>
+        <v>2938293</v>
       </c>
       <c r="M2" t="n">
-        <v>1522275</v>
+        <v>717803</v>
       </c>
       <c r="N2" t="n">
-        <v>82637</v>
+        <v>35811</v>
       </c>
       <c r="O2" t="n">
-        <v>890668</v>
+        <v>425774</v>
       </c>
       <c r="P2" t="n">
-        <v>336893</v>
+        <v>161367</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998922944068909</v>
+        <v>0.9998874068260193</v>
       </c>
       <c r="R2" t="n">
-        <v>0.966869592666626</v>
+        <v>0.946633517742157</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9116463661193848</v>
+        <v>0.8780199885368347</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9111834168434143</v>
+        <v>0.8607906699180603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3567860424518585</v>
+        <v>0.3187620043754578</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9077157974243164</v>
+        <v>0.8664597868919373</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9492163062095642</v>
+        <v>0.9272633194923401</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="D3" t="n">
-        <v>9751801</v>
+        <v>4787845</v>
       </c>
       <c r="E3" t="n">
-        <v>317426</v>
+        <v>243937</v>
       </c>
       <c r="F3" t="n">
-        <v>2650</v>
+        <v>1670</v>
       </c>
       <c r="G3" t="n">
-        <v>593</v>
+        <v>387</v>
       </c>
       <c r="H3" t="n">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>20031884</v>
+        <v>10015911</v>
       </c>
       <c r="K3" t="n">
-        <v>22252012</v>
+        <v>11025547</v>
       </c>
       <c r="L3" t="n">
-        <v>25551896</v>
+        <v>12662041</v>
       </c>
       <c r="M3" t="n">
-        <v>30647652</v>
+        <v>15281703</v>
       </c>
       <c r="N3" t="n">
-        <v>32332153</v>
+        <v>16164003</v>
       </c>
       <c r="O3" t="n">
-        <v>31550891</v>
+        <v>15755006</v>
       </c>
       <c r="P3" t="n">
-        <v>32254631</v>
+        <v>16123660</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9681094288825989</v>
+        <v>0.9510754346847534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9386337399482727</v>
+        <v>0.9014958143234253</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8170366883277893</v>
+        <v>0.7703303098678589</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4640729129314423</v>
+        <v>0.4020816385746002</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8751274943351746</v>
+        <v>0.8365355134010315</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8715492486953735</v>
+        <v>0.8348785638809204</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03184710126109398</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>306670</v>
+        <v>249043</v>
       </c>
       <c r="E4" t="n">
-        <v>6114889</v>
+        <v>2938293</v>
       </c>
       <c r="F4" t="n">
-        <v>90217</v>
+        <v>69438</v>
       </c>
       <c r="G4" t="n">
-        <v>1924</v>
+        <v>1634</v>
       </c>
       <c r="H4" t="n">
-        <v>921</v>
+        <v>900</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J4" t="n">
-        <v>1360</v>
+        <v>711</v>
       </c>
       <c r="K4" t="n">
-        <v>334152</v>
+        <v>269915</v>
       </c>
       <c r="L4" t="n">
-        <v>592634</v>
+        <v>408206</v>
       </c>
       <c r="M4" t="n">
-        <v>148382</v>
+        <v>116085</v>
       </c>
       <c r="N4" t="n">
-        <v>148978</v>
+        <v>76533</v>
       </c>
       <c r="O4" t="n">
-        <v>90551</v>
+        <v>65621</v>
       </c>
       <c r="P4" t="n">
-        <v>18024</v>
+        <v>12658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999461770057678</v>
+        <v>0.9999436736106873</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9674891233444214</v>
+        <v>0.9488493204116821</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9249432682991028</v>
+        <v>0.8896030783653259</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8615456819534302</v>
+        <v>0.8130521178245544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.403418242931366</v>
+        <v>0.3556064963340759</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8911238312721252</v>
+        <v>0.8512347340583801</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9087262749671936</v>
+        <v>0.8786491751670837</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>350</v>
+        <v>179</v>
       </c>
       <c r="D5" t="n">
-        <v>17355</v>
+        <v>12657</v>
       </c>
       <c r="E5" t="n">
-        <v>230652</v>
+        <v>144013</v>
       </c>
       <c r="F5" t="n">
-        <v>1522275</v>
+        <v>717803</v>
       </c>
       <c r="G5" t="n">
-        <v>66799</v>
+        <v>32352</v>
       </c>
       <c r="H5" t="n">
-        <v>25162</v>
+        <v>24248</v>
       </c>
       <c r="I5" t="n">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321235</v>
+        <v>246293</v>
       </c>
       <c r="L5" t="n">
-        <v>399781</v>
+        <v>321060</v>
       </c>
       <c r="M5" t="n">
-        <v>340891</v>
+        <v>214009</v>
       </c>
       <c r="N5" t="n">
-        <v>95432</v>
+        <v>53253</v>
       </c>
       <c r="O5" t="n">
-        <v>127090</v>
+        <v>83199</v>
       </c>
       <c r="P5" t="n">
-        <v>49652</v>
+        <v>31915</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999958336353302</v>
+        <v>0.999956488609314</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9799325466156006</v>
+        <v>0.9683881998062134</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9696130156517029</v>
+        <v>0.9553408622741699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9850188493728638</v>
+        <v>0.9797855615615845</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9925163388252258</v>
+        <v>0.9920520782470703</v>
       </c>
       <c r="V5" t="n">
-        <v>0.993336021900177</v>
+        <v>0.9908865094184875</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9979277849197388</v>
+        <v>0.997270405292511</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>10055</v>
+        <v>8161</v>
       </c>
       <c r="E6" t="n">
-        <v>43489</v>
+        <v>19246</v>
       </c>
       <c r="F6" t="n">
-        <v>25053</v>
+        <v>15864</v>
       </c>
       <c r="G6" t="n">
-        <v>82637</v>
+        <v>35811</v>
       </c>
       <c r="H6" t="n">
-        <v>16368</v>
+        <v>9642</v>
       </c>
       <c r="I6" t="n">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>976</v>
+        <v>933</v>
       </c>
       <c r="F7" t="n">
-        <v>30108</v>
+        <v>28796</v>
       </c>
       <c r="G7" t="n">
-        <v>78907</v>
+        <v>41652</v>
       </c>
       <c r="H7" t="n">
-        <v>890668</v>
+        <v>425774</v>
       </c>
       <c r="I7" t="n">
-        <v>16977</v>
+        <v>11736</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>458</v>
+        <v>240</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="G8" t="n">
-        <v>755</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
-        <v>47957</v>
+        <v>30749</v>
       </c>
       <c r="I8" t="n">
-        <v>336893</v>
+        <v>161367</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
